--- a/data/trans_camb/P1418-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1418-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,51</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,71</t>
+          <t>-2,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; -1,36</t>
+          <t>-5,59; -1,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,36</t>
+          <t>-4,74; -0,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,7</t>
+          <t>-3,64; 0,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -2,49</t>
+          <t>-9,35; -2,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,06; -0,63</t>
+          <t>-7,91; -0,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 0,73</t>
+          <t>-6,54; 0,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; -2,47</t>
+          <t>-6,28; -2,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -1,02</t>
+          <t>-5,14; -0,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,23</t>
+          <t>-3,84; 0,09</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-34,94%</t>
+          <t>-34,67%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-34,02%</t>
+          <t>-34,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-31,21%</t>
+          <t>-31,18%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-94,08; -35,72</t>
+          <t>-94,64; -41,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,8; 2,63</t>
+          <t>-84,21; 0,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,91; 33,72</t>
+          <t>-66,27; 28,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-87,89; -36,98</t>
+          <t>-88,85; -33,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,14; -3,97</t>
+          <t>-76,47; 4,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,72; 15,1</t>
+          <t>-59,91; 12,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-88,3; -51,1</t>
+          <t>-87,04; -49,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,7; -19,71</t>
+          <t>-72,54; -17,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-53,5; 5,01</t>
+          <t>-54,7; 1,92</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-2,3</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; -0,41</t>
+          <t>-6,07; -0,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -1,98</t>
+          <t>-6,75; -2,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; -0,11</t>
+          <t>-5,17; -0,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 2,72</t>
+          <t>-4,39; 2,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; -0,83</t>
+          <t>-6,51; -0,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 2,98</t>
+          <t>-3,34; 3,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; -0,12</t>
+          <t>-4,33; 0,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -2,02</t>
+          <t>-5,6; -2,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,69</t>
+          <t>-3,33; 0,59</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-51,01%</t>
+          <t>-48,31%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,18%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-28,04%</t>
+          <t>-24,06%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-86,94; -0,77</t>
+          <t>-88,25; -0,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-97,12; -50,15</t>
+          <t>-96,13; -46,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,83; 3,46</t>
+          <t>-73,53; 7,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,32; 67,12</t>
+          <t>-58,57; 60,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,73; -15,24</t>
+          <t>-86,78; -19,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 76,61</t>
+          <t>-44,84; 77,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 0,53</t>
+          <t>-66,82; 1,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,96; -45,87</t>
+          <t>-86,33; -42,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,83; 18,92</t>
+          <t>-50,68; 16,35</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,42</t>
+          <t>-0,86</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>1,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 0,06</t>
+          <t>-5,12; 0,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; -1,56</t>
+          <t>-6,42; -1,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,65</t>
+          <t>-3,35; 2,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 7,38</t>
+          <t>-5,12; 6,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 5,25</t>
+          <t>-8,25; 5,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 11,18</t>
+          <t>-2,04; 11,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,27</t>
+          <t>-3,63; 1,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,71; -1,02</t>
+          <t>-5,64; -0,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 1,96</t>
+          <t>-1,52; 3,67</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-42,19%</t>
+          <t>-14,99%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,28%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,72; 3,95</t>
+          <t>-67,16; 6,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-86,71; -31,89</t>
+          <t>-84,01; -25,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,99; 12,96</t>
+          <t>-48,1; 47,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 110,35</t>
+          <t>-38,74; 107,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 83,28</t>
+          <t>-63,19; 80,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 174,78</t>
+          <t>-16,75; 168,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,59; 22,81</t>
+          <t>-45,75; 25,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,25; -14,49</t>
+          <t>-69,2; -12,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,94; 31,47</t>
+          <t>-19,81; 70,56</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,51</t>
+          <t>-0,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,01</t>
+          <t>-3,77; -0,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,61; -2,3</t>
+          <t>-5,73; -2,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,91</t>
+          <t>-2,76; 1,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,7</t>
+          <t>-3,85; 1,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -0,77</t>
+          <t>-5,82; -1,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -0,07</t>
+          <t>-3,67; 1,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,02</t>
+          <t>-3,59; -0,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; -2,04</t>
+          <t>-5,13; -2,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,06</t>
+          <t>-2,44; 0,65</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-12,87%</t>
+          <t>-12,04%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-31,61%</t>
+          <t>-14,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-21,13%</t>
+          <t>-12,34%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 0,86</t>
+          <t>-50,56; -0,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,15; -38,82</t>
+          <t>-74,13; -39,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,28; 15,61</t>
+          <t>-34,77; 21,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 26,38</t>
+          <t>-41,02; 24,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,6; -11,71</t>
+          <t>-60,5; -14,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,44; -1,62</t>
+          <t>-38,51; 19,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,78; -0,77</t>
+          <t>-43,16; -0,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,86; -32,89</t>
+          <t>-63,67; -33,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 0,48</t>
+          <t>-30,97; 9,72</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -0,27</t>
+          <t>-6,74; -0,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,87</t>
+          <t>-5,89; 0,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 1,14</t>
+          <t>-6,06; 0,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 5,62</t>
+          <t>-2,12; 5,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,81</t>
+          <t>-5,1; 1,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 5,34</t>
+          <t>-1,07; 5,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,36</t>
+          <t>-2,99; 2,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,24</t>
+          <t>-4,9; 0,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,98</t>
+          <t>-2,23; 2,58</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-26,46%</t>
+          <t>-35,59%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,44; -1,85</t>
+          <t>-72,56; -14,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 17,9</t>
+          <t>-61,63; 15,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 22,47</t>
+          <t>-62,02; 11,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 60,32</t>
+          <t>-17,61; 52,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,92; 20,66</t>
+          <t>-38,9; 17,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 57,04</t>
+          <t>-8,76; 58,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 28,69</t>
+          <t>-26,83; 24,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,56; 2,92</t>
+          <t>-43,08; 1,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 35,18</t>
+          <t>-19,21; 31,52</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-3,83</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,23</t>
+          <t>-3,1</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,99</t>
+          <t>-1,24; 1,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -0,27</t>
+          <t>-2,66; -0,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 7,47</t>
+          <t>-0,89; 7,34</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,45</t>
+          <t>-2,78; 2,89</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,15</t>
+          <t>-6,06; -0,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,29; -1,51</t>
+          <t>-6,29; -1,35</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,37</t>
+          <t>-2,39; 2,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,87; -0,57</t>
+          <t>-4,84; -0,58</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,18; -0,87</t>
+          <t>-5,35; -1,02</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117,65%</t>
+          <t>101,58%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-30,33%</t>
+          <t>-30,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-30,93%</t>
+          <t>-29,63%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 20,97</t>
+          <t>-19,59; 25,58</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 1,3</t>
+          <t>-42,66; -3,64</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-44,77; -13,39</t>
+          <t>-44,53; -11,94</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 24,83</t>
+          <t>-20,43; 24,44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -5,16</t>
+          <t>-41,9; -5,78</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-45,42; -9,07</t>
+          <t>-45,55; -9,87</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-1,2</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -1,44</t>
+          <t>-3,34; -1,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -2,1</t>
+          <t>-4,09; -2,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,49</t>
+          <t>-2,28; -0,16</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,11</t>
+          <t>-1,96; 1,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,34; -1,66</t>
+          <t>-4,48; -1,62</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,43</t>
+          <t>-2,47; 0,11</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,48</t>
+          <t>-2,29; -0,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -2,18</t>
+          <t>-3,92; -2,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,68</t>
+          <t>-2,06; -0,39</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-26,19%</t>
+          <t>-22,02%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-17,83%</t>
+          <t>-12,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-20,36%</t>
+          <t>-15,22%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-55,97; -27,55</t>
+          <t>-55,0; -27,36</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-66,45; -42,99</t>
+          <t>-67,0; -43,22</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-45,83; -9,68</t>
+          <t>-36,82; -2,61</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 11,81</t>
+          <t>-17,84; 11,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,78; -17,77</t>
+          <t>-41,18; -17,1</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-34,39; -4,71</t>
+          <t>-22,59; 1,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-28,06; -6,77</t>
+          <t>-27,18; -6,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-46,86; -28,73</t>
+          <t>-46,91; -28,87</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-32,58; -9,42</t>
+          <t>-24,49; -5,0</t>
         </is>
       </c>
     </row>
